--- a/jpcore-r4b/develop/StructureDefinition-JP-Specimen.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-JP-Specimen.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-JP-Specimen.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-JP-Specimen.xlsx
@@ -416,7 +416,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -436,7 +436,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
